--- a/src/main/resources/Locations.xlsx
+++ b/src/main/resources/Locations.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180"/>
+    <workbookView windowWidth="27945" windowHeight="12180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="85">
   <si>
     <t>103</t>
   </si>
@@ -261,6 +262,27 @@
   </si>
   <si>
     <t>70198-Stanford yard-(terminal)</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>arifraza</t>
+  </si>
+  <si>
+    <t>1234567</t>
+  </si>
+  <si>
+    <t>jfelisme</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>dleonardo</t>
   </si>
 </sst>
 </file>
@@ -273,7 +295,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,13 +306,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -758,148 +773,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1500,4 +1515,52 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="10.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>